--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N78_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N78_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.55600998756858</v>
+        <v>3.177851622979894</v>
       </c>
       <c r="D2" t="n">
-        <v>35.07529080415712</v>
+        <v>5.699734755675532</v>
       </c>
       <c r="E2" t="n">
-        <v>21.54447130937484</v>
+        <v>3.500976587773412</v>
       </c>
       <c r="F2" t="n">
-        <v>21.29658474282595</v>
+        <v>3.460695020709218</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.03134353234762</v>
+        <v>2.280093324006488</v>
       </c>
       <c r="D3" t="n">
-        <v>6.758261556742039</v>
+        <v>1.098217502970581</v>
       </c>
       <c r="E3" t="n">
-        <v>21.54447130937484</v>
+        <v>3.500976587773412</v>
       </c>
       <c r="F3" t="n">
-        <v>21.29658474282595</v>
+        <v>3.460695020709218</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.14685958647638</v>
+        <v>5.223864682802412</v>
       </c>
       <c r="D4" t="n">
-        <v>30.73984768607715</v>
+        <v>4.995225248987537</v>
       </c>
       <c r="E4" t="n">
-        <v>21.54447130937484</v>
+        <v>3.500976587773412</v>
       </c>
       <c r="F4" t="n">
-        <v>21.29658474282595</v>
+        <v>3.460695020709218</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>71.43832840778347</v>
+        <v>11.60872836626482</v>
       </c>
       <c r="D5" t="n">
-        <v>69.8841755749901</v>
+        <v>11.35617853093589</v>
       </c>
       <c r="E5" t="n">
-        <v>21.54447130937484</v>
+        <v>3.500976587773412</v>
       </c>
       <c r="F5" t="n">
-        <v>21.29658474282595</v>
+        <v>3.460695020709218</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.93767283299236</v>
+        <v>8.764871835361259</v>
       </c>
       <c r="D6" t="n">
-        <v>52.81092210666908</v>
+        <v>8.581774842333726</v>
       </c>
       <c r="E6" t="n">
-        <v>21.54447130937484</v>
+        <v>3.500976587773412</v>
       </c>
       <c r="F6" t="n">
-        <v>21.29658474282595</v>
+        <v>3.460695020709218</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
